--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH219"/>
+  <dimension ref="A1:AH221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24012,6 +24012,222 @@
       <c r="AH219" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:17:23+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>425.06</v>
+      </c>
+      <c r="C220" t="n">
+        <v>440.05</v>
+      </c>
+      <c r="D220" t="n">
+        <v>445</v>
+      </c>
+      <c r="E220" t="n">
+        <v>444.35</v>
+      </c>
+      <c r="F220" t="n">
+        <v>441.96</v>
+      </c>
+      <c r="G220" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="H220" t="n">
+        <v>432.78</v>
+      </c>
+      <c r="I220" t="n">
+        <v>433.22</v>
+      </c>
+      <c r="J220" t="n">
+        <v>434.94</v>
+      </c>
+      <c r="K220" t="n">
+        <v>438.38</v>
+      </c>
+      <c r="L220" t="n">
+        <v>438.62</v>
+      </c>
+      <c r="M220" t="n">
+        <v>434.77</v>
+      </c>
+      <c r="N220" t="n">
+        <v>432.19</v>
+      </c>
+      <c r="O220" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="P220" t="n">
+        <v>424.74</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>422.24</v>
+      </c>
+      <c r="R220" t="n">
+        <v>406.98</v>
+      </c>
+      <c r="S220" t="n">
+        <v>409.71</v>
+      </c>
+      <c r="T220" t="n">
+        <v>409.22</v>
+      </c>
+      <c r="U220" t="n">
+        <v>412.29</v>
+      </c>
+      <c r="V220" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="W220" t="n">
+        <v>404.79</v>
+      </c>
+      <c r="X220" t="n">
+        <v>403.45</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>401.51</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>389.78</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>382.53</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>379.39</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>342.07</v>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>426.42</v>
+      </c>
+      <c r="C221" t="n">
+        <v>438.88</v>
+      </c>
+      <c r="D221" t="n">
+        <v>442.55</v>
+      </c>
+      <c r="E221" t="n">
+        <v>442.02</v>
+      </c>
+      <c r="F221" t="n">
+        <v>437.23</v>
+      </c>
+      <c r="G221" t="n">
+        <v>434.85</v>
+      </c>
+      <c r="H221" t="n">
+        <v>431.03</v>
+      </c>
+      <c r="I221" t="n">
+        <v>435.27</v>
+      </c>
+      <c r="J221" t="n">
+        <v>430.63</v>
+      </c>
+      <c r="K221" t="n">
+        <v>431.06</v>
+      </c>
+      <c r="L221" t="n">
+        <v>430.68</v>
+      </c>
+      <c r="M221" t="n">
+        <v>425.46</v>
+      </c>
+      <c r="N221" t="n">
+        <v>429.62</v>
+      </c>
+      <c r="O221" t="n">
+        <v>427.97</v>
+      </c>
+      <c r="P221" t="n">
+        <v>422.64</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>421.03</v>
+      </c>
+      <c r="R221" t="n">
+        <v>403.06</v>
+      </c>
+      <c r="S221" t="n">
+        <v>407.15</v>
+      </c>
+      <c r="T221" t="n">
+        <v>406.95</v>
+      </c>
+      <c r="U221" t="n">
+        <v>404.56</v>
+      </c>
+      <c r="V221" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="W221" t="n">
+        <v>399.87</v>
+      </c>
+      <c r="X221" t="n">
+        <v>400.81</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>400.47</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>393.21</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>385.39</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>353.93</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>342.07</v>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24026,7 +24242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B225"/>
+  <dimension ref="A1:B227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26279,6 +26495,26 @@
       </c>
       <c r="B225" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -26447,28 +26683,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1719819903770749</v>
+        <v>0.1867049735373812</v>
       </c>
       <c r="J2" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K2" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01495160319602007</v>
+        <v>0.01784346739029785</v>
       </c>
       <c r="M2" t="n">
-        <v>8.876494466437959</v>
+        <v>8.872893163083152</v>
       </c>
       <c r="N2" t="n">
-        <v>125.7655928551846</v>
+        <v>125.2813456896914</v>
       </c>
       <c r="O2" t="n">
-        <v>11.21452597550091</v>
+        <v>11.19291497732791</v>
       </c>
       <c r="P2" t="n">
-        <v>412.4783210759288</v>
+        <v>412.3415490264547</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26525,28 +26761,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.173732128984762</v>
+        <v>0.1957851479956613</v>
       </c>
       <c r="J3" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01639744714140223</v>
+        <v>0.02089382924963912</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1469699306367</v>
+        <v>8.184698070995701</v>
       </c>
       <c r="N3" t="n">
-        <v>116.2441885810187</v>
+        <v>116.6646574946012</v>
       </c>
       <c r="O3" t="n">
-        <v>10.78165982495361</v>
+        <v>10.8011414903519</v>
       </c>
       <c r="P3" t="n">
-        <v>421.9270558846605</v>
+        <v>421.7204358165389</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26603,28 +26839,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2777150816962454</v>
+        <v>0.2957093785077839</v>
       </c>
       <c r="J4" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K4" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02911763307691551</v>
+        <v>0.03335820417492685</v>
       </c>
       <c r="M4" t="n">
-        <v>9.695641448907153</v>
+        <v>9.696165371048593</v>
       </c>
       <c r="N4" t="n">
-        <v>162.7135692420555</v>
+        <v>162.1802157889421</v>
       </c>
       <c r="O4" t="n">
-        <v>12.75592290828286</v>
+        <v>12.73499963835657</v>
       </c>
       <c r="P4" t="n">
-        <v>425.9719999976887</v>
+        <v>425.8007621951671</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26681,28 +26917,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3327407834943192</v>
+        <v>0.3439567477412739</v>
       </c>
       <c r="J5" t="n">
+        <v>220</v>
+      </c>
+      <c r="K5" t="n">
         <v>218</v>
       </c>
-      <c r="K5" t="n">
-        <v>216</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.04238190198947778</v>
+        <v>0.04595385894908566</v>
       </c>
       <c r="M5" t="n">
-        <v>9.803238766959257</v>
+        <v>9.764285663886897</v>
       </c>
       <c r="N5" t="n">
-        <v>161.5771421580965</v>
+        <v>160.497441844461</v>
       </c>
       <c r="O5" t="n">
-        <v>12.71129978240213</v>
+        <v>12.66875849657183</v>
       </c>
       <c r="P5" t="n">
-        <v>427.6630835800988</v>
+        <v>427.5591196072156</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26759,28 +26995,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.464382357494394</v>
+        <v>0.469432229361963</v>
       </c>
       <c r="J6" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K6" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07711403064929045</v>
+        <v>0.08013438988130483</v>
       </c>
       <c r="M6" t="n">
-        <v>9.727485898466117</v>
+        <v>9.664537266293973</v>
       </c>
       <c r="N6" t="n">
-        <v>164.5060287820484</v>
+        <v>163.1060520637908</v>
       </c>
       <c r="O6" t="n">
-        <v>12.82599036262106</v>
+        <v>12.77129797881918</v>
       </c>
       <c r="P6" t="n">
-        <v>424.230149501134</v>
+        <v>424.1825419889618</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26837,28 +27073,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5608606817871024</v>
+        <v>0.563834028462129</v>
       </c>
       <c r="J7" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K7" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1265692668725208</v>
+        <v>0.1300416473937914</v>
       </c>
       <c r="M7" t="n">
-        <v>9.561817366690526</v>
+        <v>9.489710077288008</v>
       </c>
       <c r="N7" t="n">
-        <v>141.4251444995925</v>
+        <v>140.1878554400941</v>
       </c>
       <c r="O7" t="n">
-        <v>11.89223042576928</v>
+        <v>11.84009524624249</v>
       </c>
       <c r="P7" t="n">
-        <v>419.5702867877492</v>
+        <v>419.5430344932817</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26915,28 +27151,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6306563774834513</v>
+        <v>0.627530524598452</v>
       </c>
       <c r="J8" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K8" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1619623834550814</v>
+        <v>0.1634008118948901</v>
       </c>
       <c r="M8" t="n">
-        <v>9.252865203542918</v>
+        <v>9.183298358358043</v>
       </c>
       <c r="N8" t="n">
-        <v>134.5783704181128</v>
+        <v>133.3872677434345</v>
       </c>
       <c r="O8" t="n">
-        <v>11.60079180134325</v>
+        <v>11.54934057612964</v>
       </c>
       <c r="P8" t="n">
-        <v>416.8951108106803</v>
+        <v>416.9237474123344</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26993,28 +27229,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6932838444884019</v>
+        <v>0.6955681769491416</v>
       </c>
       <c r="J9" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K9" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1856367031599052</v>
+        <v>0.189785225163756</v>
       </c>
       <c r="M9" t="n">
-        <v>9.169076777792778</v>
+        <v>9.098236353155722</v>
       </c>
       <c r="N9" t="n">
-        <v>137.370329604363</v>
+        <v>136.1472879240396</v>
       </c>
       <c r="O9" t="n">
-        <v>11.7205089311157</v>
+        <v>11.66821699849808</v>
       </c>
       <c r="P9" t="n">
-        <v>414.3365356891332</v>
+        <v>414.3155807561138</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27071,28 +27307,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8435528297662986</v>
+        <v>0.8438686444829924</v>
       </c>
       <c r="J10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2584565130362541</v>
+        <v>0.2625485084092157</v>
       </c>
       <c r="M10" t="n">
-        <v>9.113835742290359</v>
+        <v>9.050578366693896</v>
       </c>
       <c r="N10" t="n">
-        <v>133.011794484077</v>
+        <v>131.8455360170736</v>
       </c>
       <c r="O10" t="n">
-        <v>11.53307393907093</v>
+        <v>11.48240114336168</v>
       </c>
       <c r="P10" t="n">
-        <v>410.0231978629063</v>
+        <v>410.0203196615552</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27149,28 +27385,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8614543679014287</v>
+        <v>0.8665677887488595</v>
       </c>
       <c r="J11" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K11" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2425293878461092</v>
+        <v>0.2483237785076577</v>
       </c>
       <c r="M11" t="n">
-        <v>9.568151828044801</v>
+        <v>9.517787597500556</v>
       </c>
       <c r="N11" t="n">
-        <v>151.0018984728716</v>
+        <v>149.8336690876441</v>
       </c>
       <c r="O11" t="n">
-        <v>12.28828297496731</v>
+        <v>12.24065639937843</v>
       </c>
       <c r="P11" t="n">
-        <v>408.6218192315554</v>
+        <v>408.5749608427097</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27227,28 +27463,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7602042033883188</v>
+        <v>0.7696566512298912</v>
       </c>
       <c r="J12" t="n">
+        <v>220</v>
+      </c>
+      <c r="K12" t="n">
         <v>218</v>
       </c>
-      <c r="K12" t="n">
-        <v>216</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1953816422173241</v>
+        <v>0.2022168854410961</v>
       </c>
       <c r="M12" t="n">
-        <v>9.794346256318009</v>
+        <v>9.753724760926422</v>
       </c>
       <c r="N12" t="n">
-        <v>151.9810533446696</v>
+        <v>151.0048788425085</v>
       </c>
       <c r="O12" t="n">
-        <v>12.3280595936534</v>
+        <v>12.28840424312728</v>
       </c>
       <c r="P12" t="n">
-        <v>408.7771757496496</v>
+        <v>408.6888265885611</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27305,28 +27541,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7194830357623631</v>
+        <v>0.7285719727784267</v>
       </c>
       <c r="J13" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K13" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L13" t="n">
-        <v>0.172365201802653</v>
+        <v>0.1785982620723472</v>
       </c>
       <c r="M13" t="n">
-        <v>10.10516630522951</v>
+        <v>10.05409281375421</v>
       </c>
       <c r="N13" t="n">
-        <v>161.9372285908932</v>
+        <v>160.9218944582163</v>
       </c>
       <c r="O13" t="n">
-        <v>12.72545592860599</v>
+        <v>12.68549937756556</v>
       </c>
       <c r="P13" t="n">
-        <v>405.4441001301302</v>
+        <v>405.3607956652485</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27383,28 +27619,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7249176483949126</v>
+        <v>0.737507993230867</v>
       </c>
       <c r="J14" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K14" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1795320747463166</v>
+        <v>0.1873136068400401</v>
       </c>
       <c r="M14" t="n">
-        <v>9.927399018505822</v>
+        <v>9.901519977566652</v>
       </c>
       <c r="N14" t="n">
-        <v>156.463607430437</v>
+        <v>155.5532007795848</v>
       </c>
       <c r="O14" t="n">
-        <v>12.50854137901126</v>
+        <v>12.47209688783666</v>
       </c>
       <c r="P14" t="n">
-        <v>404.0041086638468</v>
+        <v>403.8886698389682</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27461,28 +27697,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6535815161561815</v>
+        <v>0.6668933443752</v>
       </c>
       <c r="J15" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K15" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1518873262492558</v>
+        <v>0.1594523134990457</v>
       </c>
       <c r="M15" t="n">
-        <v>9.605801657863708</v>
+        <v>9.571369314536707</v>
       </c>
       <c r="N15" t="n">
-        <v>153.8011250522904</v>
+        <v>152.9555682623362</v>
       </c>
       <c r="O15" t="n">
-        <v>12.40165815737115</v>
+        <v>12.3675206998952</v>
       </c>
       <c r="P15" t="n">
-        <v>403.7420031020241</v>
+        <v>403.6187148520486</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27539,28 +27775,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.414079543896363</v>
+        <v>0.4307556472412795</v>
       </c>
       <c r="J16" t="n">
+        <v>220</v>
+      </c>
+      <c r="K16" t="n">
         <v>218</v>
       </c>
-      <c r="K16" t="n">
-        <v>216</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.06782311294932331</v>
+        <v>0.07402690304263559</v>
       </c>
       <c r="M16" t="n">
-        <v>9.879271587736381</v>
+        <v>9.859688702735218</v>
       </c>
       <c r="N16" t="n">
-        <v>150.4911287194539</v>
+        <v>149.968570000065</v>
       </c>
       <c r="O16" t="n">
-        <v>12.26748257465459</v>
+        <v>12.24616552232024</v>
       </c>
       <c r="P16" t="n">
-        <v>402.8551857226857</v>
+        <v>402.6992694198099</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27617,28 +27853,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.02955476277067781</v>
+        <v>0.00668108440426666</v>
       </c>
       <c r="J17" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K17" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003550584681184521</v>
+        <v>1.806790913039258e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>10.36850918334892</v>
+        <v>10.4416215655844</v>
       </c>
       <c r="N17" t="n">
-        <v>160.6987560437591</v>
+        <v>163.3402754805602</v>
       </c>
       <c r="O17" t="n">
-        <v>12.67670130766514</v>
+        <v>12.78046460347042</v>
       </c>
       <c r="P17" t="n">
-        <v>400.9005473851897</v>
+        <v>400.5693082178454</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27695,28 +27931,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2314342528370372</v>
+        <v>0.2543011512305682</v>
       </c>
       <c r="J18" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K18" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0131710301942376</v>
+        <v>0.01608502400924183</v>
       </c>
       <c r="M18" t="n">
-        <v>13.15622480712823</v>
+        <v>13.13424987344131</v>
       </c>
       <c r="N18" t="n">
-        <v>261.453134188811</v>
+        <v>260.7500117936406</v>
       </c>
       <c r="O18" t="n">
-        <v>16.16951249075899</v>
+        <v>16.14775562713409</v>
       </c>
       <c r="P18" t="n">
-        <v>385.1983469637253</v>
+        <v>384.9886809368309</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27773,28 +28009,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2324477814029485</v>
+        <v>0.2557555957848329</v>
       </c>
       <c r="J19" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K19" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01461495883262465</v>
+        <v>0.01787473725785871</v>
       </c>
       <c r="M19" t="n">
-        <v>12.00171635998926</v>
+        <v>12.00552745428425</v>
       </c>
       <c r="N19" t="n">
-        <v>237.34255587755</v>
+        <v>236.9023296684461</v>
       </c>
       <c r="O19" t="n">
-        <v>15.4059259987042</v>
+        <v>15.39163180655145</v>
       </c>
       <c r="P19" t="n">
-        <v>388.3175804807113</v>
+        <v>388.1038658613944</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27851,28 +28087,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5628553147656732</v>
+        <v>0.5808827298427786</v>
       </c>
       <c r="J20" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K20" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1282100819821785</v>
+        <v>0.1370166914578262</v>
       </c>
       <c r="M20" t="n">
-        <v>9.316625982011983</v>
+        <v>9.315470168813318</v>
       </c>
       <c r="N20" t="n">
-        <v>138.0854521027489</v>
+        <v>137.8173467101231</v>
       </c>
       <c r="O20" t="n">
-        <v>11.75097664463465</v>
+        <v>11.73956331002662</v>
       </c>
       <c r="P20" t="n">
-        <v>382.4842574586332</v>
+        <v>382.3154836144578</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27929,28 +28165,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5588234932469283</v>
+        <v>0.5786004292407936</v>
       </c>
       <c r="J21" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K21" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1487358972711734</v>
+        <v>0.1589514439428186</v>
       </c>
       <c r="M21" t="n">
-        <v>8.265036243731982</v>
+        <v>8.279458727884677</v>
       </c>
       <c r="N21" t="n">
-        <v>115.33255846829</v>
+        <v>115.6032359739195</v>
       </c>
       <c r="O21" t="n">
-        <v>10.73929971964141</v>
+        <v>10.75189452951988</v>
       </c>
       <c r="P21" t="n">
-        <v>381.9448913153664</v>
+        <v>381.7592622428635</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28007,28 +28243,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4064622352766584</v>
+        <v>0.4287185313806011</v>
       </c>
       <c r="J22" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K22" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08957943871625451</v>
+        <v>0.09910989185825614</v>
       </c>
       <c r="M22" t="n">
-        <v>8.071874574903916</v>
+        <v>8.113815024562269</v>
       </c>
       <c r="N22" t="n">
-        <v>110.3518434681267</v>
+        <v>111.0382271868441</v>
       </c>
       <c r="O22" t="n">
-        <v>10.50484856950002</v>
+        <v>10.53746777868593</v>
       </c>
       <c r="P22" t="n">
-        <v>383.2153640903748</v>
+        <v>383.0101019382764</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28085,28 +28321,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3366760498048135</v>
+        <v>0.3569426388852084</v>
       </c>
       <c r="J23" t="n">
+        <v>220</v>
+      </c>
+      <c r="K23" t="n">
         <v>218</v>
       </c>
-      <c r="K23" t="n">
-        <v>216</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06129527110708799</v>
+        <v>0.06896123241797736</v>
       </c>
       <c r="M23" t="n">
-        <v>8.019602121671822</v>
+        <v>8.053810671485152</v>
       </c>
       <c r="N23" t="n">
-        <v>110.8534508003985</v>
+        <v>111.1447909915691</v>
       </c>
       <c r="O23" t="n">
-        <v>10.52869653852738</v>
+        <v>10.54252298985253</v>
       </c>
       <c r="P23" t="n">
-        <v>381.459406248383</v>
+        <v>381.2699299228177</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28163,28 +28399,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5618624825589172</v>
+        <v>0.579076188227484</v>
       </c>
       <c r="J24" t="n">
+        <v>220</v>
+      </c>
+      <c r="K24" t="n">
         <v>218</v>
       </c>
-      <c r="K24" t="n">
-        <v>216</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.1707783568667712</v>
+        <v>0.1812014676683595</v>
       </c>
       <c r="M24" t="n">
-        <v>7.997188695609808</v>
+        <v>8.02383434120652</v>
       </c>
       <c r="N24" t="n">
-        <v>97.88600436145883</v>
+        <v>97.90756759625488</v>
       </c>
       <c r="O24" t="n">
-        <v>9.89373561206579</v>
+        <v>9.894825293872291</v>
       </c>
       <c r="P24" t="n">
-        <v>377.021263423427</v>
+        <v>376.8603226857264</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28241,28 +28477,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4672410719831824</v>
+        <v>0.4874374488511218</v>
       </c>
       <c r="J25" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K25" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1265306207142713</v>
+        <v>0.1371050594604594</v>
       </c>
       <c r="M25" t="n">
-        <v>8.259621568100979</v>
+        <v>8.298728972422387</v>
       </c>
       <c r="N25" t="n">
-        <v>97.48525145002463</v>
+        <v>97.86391724117229</v>
       </c>
       <c r="O25" t="n">
-        <v>9.873461978962832</v>
+        <v>9.892619331661978</v>
       </c>
       <c r="P25" t="n">
-        <v>376.5330712496574</v>
+        <v>376.3464355407241</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28319,28 +28555,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3164596388664913</v>
+        <v>0.3325855557105284</v>
       </c>
       <c r="J26" t="n">
+        <v>220</v>
+      </c>
+      <c r="K26" t="n">
         <v>218</v>
       </c>
-      <c r="K26" t="n">
-        <v>216</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.06350345275215241</v>
+        <v>0.07044775729548547</v>
       </c>
       <c r="M26" t="n">
-        <v>8.200534311670159</v>
+        <v>8.220132636961605</v>
       </c>
       <c r="N26" t="n">
-        <v>95.8884033880658</v>
+        <v>95.86824088184432</v>
       </c>
       <c r="O26" t="n">
-        <v>9.792262424387216</v>
+        <v>9.791232858115688</v>
       </c>
       <c r="P26" t="n">
-        <v>377.4647056342101</v>
+        <v>377.315869558436</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28397,28 +28633,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04245782135440915</v>
+        <v>0.05365987919300892</v>
       </c>
       <c r="J27" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K27" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001119453277388605</v>
+        <v>0.001816862422402976</v>
       </c>
       <c r="M27" t="n">
-        <v>8.502205076679958</v>
+        <v>8.496286401745508</v>
       </c>
       <c r="N27" t="n">
-        <v>104.0465874280573</v>
+        <v>103.530410897148</v>
       </c>
       <c r="O27" t="n">
-        <v>10.20032290802881</v>
+        <v>10.17498947896989</v>
       </c>
       <c r="P27" t="n">
-        <v>379.8173485255861</v>
+        <v>379.7138455353332</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28475,28 +28711,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.03652037048504778</v>
+        <v>-0.02757809546086133</v>
       </c>
       <c r="J28" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K28" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0007321363856437335</v>
+        <v>0.0004254006673450883</v>
       </c>
       <c r="M28" t="n">
-        <v>8.838381383242435</v>
+        <v>8.803659752241748</v>
       </c>
       <c r="N28" t="n">
-        <v>117.7511414579288</v>
+        <v>116.9569289043773</v>
       </c>
       <c r="O28" t="n">
-        <v>10.85131980258295</v>
+        <v>10.81466268102604</v>
       </c>
       <c r="P28" t="n">
-        <v>376.3218928375805</v>
+        <v>376.2392705577668</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -28553,28 +28789,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.03432559669001194</v>
+        <v>-0.02013545486370998</v>
       </c>
       <c r="J29" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K29" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0004982555721367854</v>
+        <v>0.0001743557006450569</v>
       </c>
       <c r="M29" t="n">
-        <v>10.15029795528349</v>
+        <v>10.12419732817744</v>
       </c>
       <c r="N29" t="n">
-        <v>152.8876586024249</v>
+        <v>152.1568049074548</v>
       </c>
       <c r="O29" t="n">
-        <v>12.36477491111039</v>
+        <v>12.33518564543943</v>
       </c>
       <c r="P29" t="n">
-        <v>369.8156551365873</v>
+        <v>369.6845375814594</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28631,28 +28867,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.05840559343666834</v>
+        <v>-0.04174376051662288</v>
       </c>
       <c r="J30" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K30" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0009875236030043588</v>
+        <v>0.0005132461719000725</v>
       </c>
       <c r="M30" t="n">
-        <v>12.52615623050217</v>
+        <v>12.50565660067131</v>
       </c>
       <c r="N30" t="n">
-        <v>223.2220828358344</v>
+        <v>222.0827540683958</v>
       </c>
       <c r="O30" t="n">
-        <v>14.94061855599809</v>
+        <v>14.90244121170742</v>
       </c>
       <c r="P30" t="n">
-        <v>359.8550333122656</v>
+        <v>359.7010735632441</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28709,28 +28945,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2655679816668012</v>
+        <v>-0.2454691605515048</v>
       </c>
       <c r="J31" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K31" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02517278794085109</v>
+        <v>0.02186680939336916</v>
       </c>
       <c r="M31" t="n">
-        <v>10.93162398681643</v>
+        <v>10.93269059477503</v>
       </c>
       <c r="N31" t="n">
-        <v>176.6658466985766</v>
+        <v>176.3952237258164</v>
       </c>
       <c r="O31" t="n">
-        <v>13.2915705128693</v>
+        <v>13.2813863630954</v>
       </c>
       <c r="P31" t="n">
-        <v>352.243754325329</v>
+        <v>352.0580414783374</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28787,28 +29023,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3439350346365366</v>
+        <v>-0.3135828758409935</v>
       </c>
       <c r="J32" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K32" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L32" t="n">
-        <v>0.07653567652901727</v>
+        <v>0.06385963134731976</v>
       </c>
       <c r="M32" t="n">
-        <v>7.897263865769813</v>
+        <v>7.985511899300771</v>
       </c>
       <c r="N32" t="n">
-        <v>92.32384373978894</v>
+        <v>94.34081285011435</v>
       </c>
       <c r="O32" t="n">
-        <v>9.608529738715957</v>
+        <v>9.712919893117329</v>
       </c>
       <c r="P32" t="n">
-        <v>351.5345115057788</v>
+        <v>351.2540191930457</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28865,28 +29101,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7789578569772927</v>
+        <v>-0.7551079169187035</v>
       </c>
       <c r="J33" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K33" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2147793397920945</v>
+        <v>0.2058482662729182</v>
       </c>
       <c r="M33" t="n">
-        <v>9.460681846363766</v>
+        <v>9.463548791306392</v>
       </c>
       <c r="N33" t="n">
-        <v>146.8380123043224</v>
+        <v>147.2781976979633</v>
       </c>
       <c r="O33" t="n">
-        <v>12.11767355164853</v>
+        <v>12.1358229097974</v>
       </c>
       <c r="P33" t="n">
-        <v>348.7725352771175</v>
+        <v>348.5548058313457</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28924,7 +29160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH219"/>
+  <dimension ref="A1:AH221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66331,6 +66567,350 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:17:23+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>-35.29147477558444,173.15956362085467</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>-35.290985900548925,173.15887457641108</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>-35.290440545052505,173.15827183021827</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-35.289863685082565,173.1577172181725</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-35.28927703358019,173.15717756187877</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-35.288680703169916,173.15665268923402</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-35.28807896893882,173.15613606767698</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-35.287508224284515,173.1555720863675</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-35.28694467543113,173.15499710331486</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-35.286390797224385,173.1544073368</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-35.285818915247226,173.15384507474468</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-35.285224023645256,173.15331796639242</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-35.28463696282047,173.15278060433283</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-35.28405764311209,173.15223922910636</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-35.283463682066554,173.15171715386145</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>-35.28288355457839,173.1511668795818</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>-35.2822302076834,173.1507248460992</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>-35.281680081936116,173.15013020601143</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>-35.28111147622014,173.14956288059983</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>-35.28056329322617,173.14896535662518</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>-35.27999066310631,173.14840396915866</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>-35.27938865169133,173.14788601285562</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>-35.27881515325006,173.14732589745117</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>-35.27823820828762,173.1467708715131</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>-35.277650816850674,173.14623128369726</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>-35.277043210905425,173.14573128297337</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>-35.27645918262205,173.1451959934439</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>-35.275904739822565,173.1446099526473</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>-35.275311650263745,173.14407147645005</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>-35.27471357585169,173.14353951281717</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>-35.2741781695533,173.14292561268232</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>-35.2735296567595,173.1424595826747</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>-35.29148242574197,173.15955193110196</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>-35.290979319202954,173.15888463301462</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>-35.29042676367015,173.1582928888445</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-35.28985057876498,173.15773724527236</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-35.28925042730259,173.15721821756475</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-35.28866382822256,173.1566784749644</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-35.28806912525918,173.15615110928235</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-35.28751975539714,173.15555446626752</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-35.28692043207543,173.15503414834185</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-35.28634962308845,173.15447025293972</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-35.2857742538856,173.15391331956755</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-35.28517165644036,173.15339798607835</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-35.28462248154034,173.1528026685809</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-35.284044951230186,173.15225824978702</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-35.28345163238659,173.15173496797635</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>-35.282876611696956,173.15117714386278</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>-35.28220771510393,173.15075809877098</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>-35.2816653929752,173.15015192196915</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>-35.28109845130057,173.14958213647193</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>-35.280518939844384,173.14903092813523</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>-35.27994705583063,173.1484684376562</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>-35.27936042182911,173.1479277475358</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>-35.2788000055862,173.14734829158326</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>-35.27823224105195,173.1467796934087</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>-35.27762476767285,173.14626979448684</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>-35.27701738607022,173.14576786722122</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>-35.276436170023274,173.1452266538099</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>-35.2758790314398,173.14464356365872</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>-35.2752868645152,173.14410388118858</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>-35.27467538255151,173.14358944644525</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>-35.2741781695533,173.14292561268232</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>-35.2735296567595,173.1424595826747</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH221"/>
+  <dimension ref="A1:AH222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24151,7 +24151,7 @@
         <v>431.03</v>
       </c>
       <c r="I221" t="n">
-        <v>435.27</v>
+        <v>430.17</v>
       </c>
       <c r="J221" t="n">
         <v>430.63</v>
@@ -24166,13 +24166,13 @@
         <v>425.46</v>
       </c>
       <c r="N221" t="n">
-        <v>429.62</v>
+        <v>421.45</v>
       </c>
       <c r="O221" t="n">
-        <v>427.97</v>
+        <v>419.4</v>
       </c>
       <c r="P221" t="n">
-        <v>422.64</v>
+        <v>415.51</v>
       </c>
       <c r="Q221" t="n">
         <v>421.03</v>
@@ -24181,10 +24181,10 @@
         <v>403.06</v>
       </c>
       <c r="S221" t="n">
-        <v>407.15</v>
+        <v>397.19</v>
       </c>
       <c r="T221" t="n">
-        <v>406.95</v>
+        <v>401.12</v>
       </c>
       <c r="U221" t="n">
         <v>404.56</v>
@@ -24220,14 +24220,122 @@
         <v>353.93</v>
       </c>
       <c r="AF221" t="n">
-        <v>360.3</v>
+        <v>351.61</v>
       </c>
       <c r="AG221" t="n">
-        <v>342.07</v>
+        <v>334.28</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>423.59</v>
+      </c>
+      <c r="C222" t="n">
+        <v>436.07</v>
+      </c>
+      <c r="D222" t="n">
+        <v>441.39</v>
+      </c>
+      <c r="E222" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="F222" t="n">
+        <v>437.37</v>
+      </c>
+      <c r="G222" t="n">
+        <v>434.24</v>
+      </c>
+      <c r="H222" t="n">
+        <v>430.02</v>
+      </c>
+      <c r="I222" t="n">
+        <v>427.81</v>
+      </c>
+      <c r="J222" t="n">
+        <v>427.91</v>
+      </c>
+      <c r="K222" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="L222" t="n">
+        <v>427.36</v>
+      </c>
+      <c r="M222" t="n">
+        <v>422.11</v>
+      </c>
+      <c r="N222" t="n">
+        <v>418.56</v>
+      </c>
+      <c r="O222" t="n">
+        <v>416.95</v>
+      </c>
+      <c r="P222" t="n">
+        <v>415.12</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>420.54</v>
+      </c>
+      <c r="R222" t="n">
+        <v>404.74</v>
+      </c>
+      <c r="S222" t="n">
+        <v>397.19</v>
+      </c>
+      <c r="T222" t="n">
+        <v>401.69</v>
+      </c>
+      <c r="U222" t="n">
+        <v>403.36</v>
+      </c>
+      <c r="V222" t="n">
+        <v>401.78</v>
+      </c>
+      <c r="W222" t="n">
+        <v>398.9</v>
+      </c>
+      <c r="X222" t="n">
+        <v>399.07</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>399.23</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>386.88</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>368.38</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>354.64</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>351.15</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24242,7 +24350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26515,6 +26623,16 @@
       </c>
       <c r="B227" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -26683,28 +26801,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1867049735373812</v>
+        <v>0.1919769029493738</v>
       </c>
       <c r="J2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01784346739029785</v>
+        <v>0.01901202789466272</v>
       </c>
       <c r="M2" t="n">
-        <v>8.872893163083152</v>
+        <v>8.860485882500386</v>
       </c>
       <c r="N2" t="n">
-        <v>125.2813456896914</v>
+        <v>124.8822475129827</v>
       </c>
       <c r="O2" t="n">
-        <v>11.19291497732791</v>
+        <v>11.17507259542338</v>
       </c>
       <c r="P2" t="n">
-        <v>412.3415490264547</v>
+        <v>412.29229336373</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26761,28 +26879,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1957851479956613</v>
+        <v>0.203525928036638</v>
       </c>
       <c r="J3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02089382924963912</v>
+        <v>0.02269744027772069</v>
       </c>
       <c r="M3" t="n">
-        <v>8.184698070995701</v>
+        <v>8.186940742267261</v>
       </c>
       <c r="N3" t="n">
-        <v>116.6646574946012</v>
+        <v>116.5014284936553</v>
       </c>
       <c r="O3" t="n">
-        <v>10.8011414903519</v>
+        <v>10.79358274594934</v>
       </c>
       <c r="P3" t="n">
-        <v>421.7204358165389</v>
+        <v>421.647488919</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26839,28 +26957,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2957093785077839</v>
+        <v>0.3023055213316399</v>
       </c>
       <c r="J4" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03335820417492685</v>
+        <v>0.03510409656001723</v>
       </c>
       <c r="M4" t="n">
-        <v>9.696165371048593</v>
+        <v>9.684565141110831</v>
       </c>
       <c r="N4" t="n">
-        <v>162.1802157889421</v>
+        <v>161.6911952742067</v>
       </c>
       <c r="O4" t="n">
-        <v>12.73499963835657</v>
+        <v>12.71578527949441</v>
       </c>
       <c r="P4" t="n">
-        <v>425.8007621951671</v>
+        <v>425.7376278341754</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26917,28 +27035,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3439567477412739</v>
+        <v>0.3480047214405006</v>
       </c>
       <c r="J5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04595385894908566</v>
+        <v>0.04742627756776463</v>
       </c>
       <c r="M5" t="n">
-        <v>9.764285663886897</v>
+        <v>9.737821959367286</v>
       </c>
       <c r="N5" t="n">
-        <v>160.497441844461</v>
+        <v>159.8682743325695</v>
       </c>
       <c r="O5" t="n">
-        <v>12.66875849657183</v>
+        <v>12.64390265434567</v>
       </c>
       <c r="P5" t="n">
-        <v>427.5591196072156</v>
+        <v>427.5213777208407</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26995,28 +27113,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.469432229361963</v>
+        <v>0.4699179577148262</v>
       </c>
       <c r="J6" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K6" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08013438988130483</v>
+        <v>0.08105276634215941</v>
       </c>
       <c r="M6" t="n">
-        <v>9.664537266293973</v>
+        <v>9.622404250696059</v>
       </c>
       <c r="N6" t="n">
-        <v>163.1060520637908</v>
+        <v>162.3524041974941</v>
       </c>
       <c r="O6" t="n">
-        <v>12.77129797881918</v>
+        <v>12.74175828516199</v>
       </c>
       <c r="P6" t="n">
-        <v>424.1825419889618</v>
+        <v>424.1779345099526</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27073,28 +27191,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.563834028462129</v>
+        <v>0.5634520125952284</v>
       </c>
       <c r="J7" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K7" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1300416473937914</v>
+        <v>0.1310573782988899</v>
       </c>
       <c r="M7" t="n">
-        <v>9.489710077288008</v>
+        <v>9.448975076424865</v>
       </c>
       <c r="N7" t="n">
-        <v>140.1878554400941</v>
+        <v>139.554454774474</v>
       </c>
       <c r="O7" t="n">
-        <v>11.84009524624249</v>
+        <v>11.81331684051833</v>
       </c>
       <c r="P7" t="n">
-        <v>419.5430344932817</v>
+        <v>419.546557745629</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27151,28 +27269,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.627530524598452</v>
+        <v>0.6243844888441658</v>
       </c>
       <c r="J8" t="n">
+        <v>221</v>
+      </c>
+      <c r="K8" t="n">
         <v>220</v>
       </c>
-      <c r="K8" t="n">
-        <v>219</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1634008118948901</v>
+        <v>0.163368178435357</v>
       </c>
       <c r="M8" t="n">
-        <v>9.183298358358043</v>
+        <v>9.156642588537697</v>
       </c>
       <c r="N8" t="n">
-        <v>133.3872677434345</v>
+        <v>132.8446184847469</v>
       </c>
       <c r="O8" t="n">
-        <v>11.54934057612964</v>
+        <v>11.52582398289801</v>
       </c>
       <c r="P8" t="n">
-        <v>416.9237474123344</v>
+        <v>416.9527297375096</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27229,28 +27347,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6955681769491416</v>
+        <v>0.6870039406130852</v>
       </c>
       <c r="J9" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K9" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L9" t="n">
-        <v>0.189785225163756</v>
+        <v>0.1874299731718583</v>
       </c>
       <c r="M9" t="n">
-        <v>9.098236353155722</v>
+        <v>9.080126796076462</v>
       </c>
       <c r="N9" t="n">
-        <v>136.1472879240396</v>
+        <v>135.6564423237713</v>
       </c>
       <c r="O9" t="n">
-        <v>11.66821699849808</v>
+        <v>11.64716456154764</v>
       </c>
       <c r="P9" t="n">
-        <v>414.3155807561138</v>
+        <v>414.3943602820586</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27307,28 +27425,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8438686444829924</v>
+        <v>0.8398677891411656</v>
       </c>
       <c r="J10" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K10" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2625485084092157</v>
+        <v>0.2625536132068799</v>
       </c>
       <c r="M10" t="n">
-        <v>9.050578366693896</v>
+        <v>9.032065146019308</v>
       </c>
       <c r="N10" t="n">
-        <v>131.8455360170736</v>
+        <v>131.3513422055732</v>
       </c>
       <c r="O10" t="n">
-        <v>11.48240114336168</v>
+        <v>11.46086132040577</v>
       </c>
       <c r="P10" t="n">
-        <v>410.0203196615552</v>
+        <v>410.0572187126043</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27385,28 +27503,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8665677887488595</v>
+        <v>0.8632559414663933</v>
       </c>
       <c r="J11" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K11" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2483237785076577</v>
+        <v>0.2487313669982766</v>
       </c>
       <c r="M11" t="n">
-        <v>9.517787597500556</v>
+        <v>9.490306337614781</v>
       </c>
       <c r="N11" t="n">
-        <v>149.8336690876441</v>
+        <v>149.2258507407212</v>
       </c>
       <c r="O11" t="n">
-        <v>12.24065639937843</v>
+        <v>12.21580331950057</v>
       </c>
       <c r="P11" t="n">
-        <v>408.5749608427097</v>
+        <v>408.6055053167038</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27463,28 +27581,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7696566512298912</v>
+        <v>0.7679451582337876</v>
       </c>
       <c r="J12" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2022168854410961</v>
+        <v>0.2031565276758275</v>
       </c>
       <c r="M12" t="n">
-        <v>9.753724760926422</v>
+        <v>9.718380872307597</v>
       </c>
       <c r="N12" t="n">
-        <v>151.0048788425085</v>
+        <v>150.3335898147361</v>
       </c>
       <c r="O12" t="n">
-        <v>12.28840424312728</v>
+        <v>12.26105989768976</v>
       </c>
       <c r="P12" t="n">
-        <v>408.6888265885611</v>
+        <v>408.7049204714501</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27541,28 +27659,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7285719727784267</v>
+        <v>0.7262113617462511</v>
       </c>
       <c r="J13" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K13" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1785982620723472</v>
+        <v>0.1791266740599947</v>
       </c>
       <c r="M13" t="n">
-        <v>10.05409281375421</v>
+        <v>10.02324963207609</v>
       </c>
       <c r="N13" t="n">
-        <v>160.9218944582163</v>
+        <v>160.2293870704108</v>
       </c>
       <c r="O13" t="n">
-        <v>12.68549937756556</v>
+        <v>12.65817471322034</v>
       </c>
       <c r="P13" t="n">
-        <v>405.3607956652485</v>
+        <v>405.3825670864926</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27619,28 +27737,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.737507993230867</v>
+        <v>0.7264468755967405</v>
       </c>
       <c r="J14" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K14" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1873136068400401</v>
+        <v>0.1843329772085383</v>
       </c>
       <c r="M14" t="n">
-        <v>9.901519977566652</v>
+        <v>9.863485209189077</v>
       </c>
       <c r="N14" t="n">
-        <v>155.5532007795848</v>
+        <v>154.8166973589691</v>
       </c>
       <c r="O14" t="n">
-        <v>12.47209688783666</v>
+        <v>12.44253580902901</v>
       </c>
       <c r="P14" t="n">
-        <v>403.8886698389682</v>
+        <v>403.9903531450757</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27697,28 +27815,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6668933443752</v>
+        <v>0.6558669411850661</v>
       </c>
       <c r="J15" t="n">
+        <v>221</v>
+      </c>
+      <c r="K15" t="n">
         <v>220</v>
       </c>
-      <c r="K15" t="n">
-        <v>219</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1594523134990457</v>
+        <v>0.1564715925552647</v>
       </c>
       <c r="M15" t="n">
-        <v>9.571369314536707</v>
+        <v>9.541170436178676</v>
       </c>
       <c r="N15" t="n">
-        <v>152.9555682623362</v>
+        <v>152.1716556145727</v>
       </c>
       <c r="O15" t="n">
-        <v>12.3675206998952</v>
+        <v>12.33578759603831</v>
       </c>
       <c r="P15" t="n">
-        <v>403.6187148520486</v>
+        <v>403.7210794463263</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27775,28 +27893,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4307556472412795</v>
+        <v>0.4254614596553496</v>
       </c>
       <c r="J16" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K16" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07402690304263559</v>
+        <v>0.07319282543271821</v>
       </c>
       <c r="M16" t="n">
-        <v>9.859688702735218</v>
+        <v>9.791918328904119</v>
       </c>
       <c r="N16" t="n">
-        <v>149.968570000065</v>
+        <v>148.9685886113797</v>
       </c>
       <c r="O16" t="n">
-        <v>12.24616552232024</v>
+        <v>12.20526888730354</v>
       </c>
       <c r="P16" t="n">
-        <v>402.6992694198099</v>
+        <v>402.7487580305618</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27853,28 +27971,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00668108440426666</v>
+        <v>0.02325414055574002</v>
       </c>
       <c r="J17" t="n">
+        <v>221</v>
+      </c>
+      <c r="K17" t="n">
         <v>220</v>
       </c>
-      <c r="K17" t="n">
-        <v>219</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.806790913039258e-05</v>
+        <v>0.0002187603029941698</v>
       </c>
       <c r="M17" t="n">
-        <v>10.4416215655844</v>
+        <v>10.47309777108337</v>
       </c>
       <c r="N17" t="n">
-        <v>163.3402754805602</v>
+        <v>164.3515082539523</v>
       </c>
       <c r="O17" t="n">
-        <v>12.78046460347042</v>
+        <v>12.81996522046579</v>
       </c>
       <c r="P17" t="n">
-        <v>400.5693082178454</v>
+        <v>400.416928410029</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27931,28 +28049,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2543011512305682</v>
+        <v>0.2650847137530387</v>
       </c>
       <c r="J18" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K18" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01608502400924183</v>
+        <v>0.01758200366640672</v>
       </c>
       <c r="M18" t="n">
-        <v>13.13424987344131</v>
+        <v>13.12025941541479</v>
       </c>
       <c r="N18" t="n">
-        <v>260.7500117936406</v>
+        <v>260.313998956075</v>
       </c>
       <c r="O18" t="n">
-        <v>16.14775562713409</v>
+        <v>16.13424925294248</v>
       </c>
       <c r="P18" t="n">
-        <v>384.9886809368309</v>
+        <v>384.8892263977357</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28009,28 +28127,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2557555957848329</v>
+        <v>0.2493614241395408</v>
       </c>
       <c r="J19" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K19" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01787473725785871</v>
+        <v>0.01722578368645944</v>
       </c>
       <c r="M19" t="n">
-        <v>12.00552745428425</v>
+        <v>11.9201778947056</v>
       </c>
       <c r="N19" t="n">
-        <v>236.9023296684461</v>
+        <v>235.1979409370248</v>
       </c>
       <c r="O19" t="n">
-        <v>15.39163180655145</v>
+        <v>15.33616447932875</v>
       </c>
       <c r="P19" t="n">
-        <v>388.1038658613944</v>
+        <v>388.1624344863433</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28087,28 +28205,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5808827298427786</v>
+        <v>0.5791668331038166</v>
       </c>
       <c r="J20" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K20" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1370166914578262</v>
+        <v>0.1377725611311115</v>
       </c>
       <c r="M20" t="n">
-        <v>9.315470168813318</v>
+        <v>9.264029877939583</v>
       </c>
       <c r="N20" t="n">
-        <v>137.8173467101231</v>
+        <v>136.9153751598266</v>
       </c>
       <c r="O20" t="n">
-        <v>11.73956331002662</v>
+        <v>11.70108435829033</v>
       </c>
       <c r="P20" t="n">
-        <v>382.3154836144578</v>
+        <v>382.3313967771178</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28165,28 +28283,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5786004292407936</v>
+        <v>0.5837680927656032</v>
       </c>
       <c r="J21" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K21" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1589514439428186</v>
+        <v>0.1625392421180822</v>
       </c>
       <c r="M21" t="n">
-        <v>8.279458727884677</v>
+        <v>8.264547284393213</v>
       </c>
       <c r="N21" t="n">
-        <v>115.6032359739195</v>
+        <v>115.2300262723986</v>
       </c>
       <c r="O21" t="n">
-        <v>10.75189452951988</v>
+        <v>10.73452496724464</v>
       </c>
       <c r="P21" t="n">
-        <v>381.7592622428635</v>
+        <v>381.7104634381947</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28243,28 +28361,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4287185313806011</v>
+        <v>0.4347977983254425</v>
       </c>
       <c r="J22" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K22" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09910989185825614</v>
+        <v>0.1023880660776687</v>
       </c>
       <c r="M22" t="n">
-        <v>8.113815024562269</v>
+        <v>8.107830791938174</v>
       </c>
       <c r="N22" t="n">
-        <v>111.0382271868441</v>
+        <v>110.7626309324229</v>
       </c>
       <c r="O22" t="n">
-        <v>10.53746777868593</v>
+        <v>10.5243826865248</v>
       </c>
       <c r="P22" t="n">
-        <v>383.0101019382764</v>
+        <v>382.9536905800075</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28321,28 +28439,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3569426388852084</v>
+        <v>0.3637727884296957</v>
       </c>
       <c r="J23" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K23" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06896123241797736</v>
+        <v>0.07195225105559377</v>
       </c>
       <c r="M23" t="n">
-        <v>8.053810671485152</v>
+        <v>8.052915402641236</v>
       </c>
       <c r="N23" t="n">
-        <v>111.1447909915691</v>
+        <v>110.9276292239788</v>
       </c>
       <c r="O23" t="n">
-        <v>10.54252298985253</v>
+        <v>10.53221862780956</v>
       </c>
       <c r="P23" t="n">
-        <v>381.2699299228177</v>
+        <v>381.2057031762673</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28399,28 +28517,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.579076188227484</v>
+        <v>0.5847273060118066</v>
       </c>
       <c r="J24" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K24" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1812014676683595</v>
+        <v>0.1853587501360103</v>
       </c>
       <c r="M24" t="n">
-        <v>8.02383434120652</v>
+        <v>8.019582436023363</v>
       </c>
       <c r="N24" t="n">
-        <v>97.90756759625488</v>
+        <v>97.659260702971</v>
       </c>
       <c r="O24" t="n">
-        <v>9.894825293872291</v>
+        <v>9.882270017712074</v>
       </c>
       <c r="P24" t="n">
-        <v>376.8603226857264</v>
+        <v>376.8071828668548</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28477,28 +28595,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4874374488511218</v>
+        <v>0.4956614079625534</v>
       </c>
       <c r="J25" t="n">
+        <v>221</v>
+      </c>
+      <c r="K25" t="n">
         <v>220</v>
       </c>
-      <c r="K25" t="n">
-        <v>219</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1371050594604594</v>
+        <v>0.1418337653470392</v>
       </c>
       <c r="M25" t="n">
-        <v>8.298728972422387</v>
+        <v>8.307516187832256</v>
       </c>
       <c r="N25" t="n">
-        <v>97.86391724117229</v>
+        <v>97.84775565113364</v>
       </c>
       <c r="O25" t="n">
-        <v>9.892619331661978</v>
+        <v>9.891802447033283</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3464355407241</v>
+        <v>376.2699978494056</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28555,28 +28673,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3325855557105284</v>
+        <v>0.3384257730070798</v>
       </c>
       <c r="J26" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K26" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07044775729548547</v>
+        <v>0.07330617772968173</v>
       </c>
       <c r="M26" t="n">
-        <v>8.220132636961605</v>
+        <v>8.217019555424216</v>
       </c>
       <c r="N26" t="n">
-        <v>95.86824088184432</v>
+        <v>95.64784719891146</v>
       </c>
       <c r="O26" t="n">
-        <v>9.791232858115688</v>
+        <v>9.779971738144823</v>
       </c>
       <c r="P26" t="n">
-        <v>377.315869558436</v>
+        <v>377.2616467476362</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28633,28 +28751,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05365987919300892</v>
+        <v>0.05847554464669615</v>
       </c>
       <c r="J27" t="n">
+        <v>221</v>
+      </c>
+      <c r="K27" t="n">
         <v>220</v>
       </c>
-      <c r="K27" t="n">
-        <v>219</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.001816862422402976</v>
+        <v>0.00217612068331674</v>
       </c>
       <c r="M27" t="n">
-        <v>8.496286401745508</v>
+        <v>8.488733474350008</v>
       </c>
       <c r="N27" t="n">
-        <v>103.530410897148</v>
+        <v>103.2068049012153</v>
       </c>
       <c r="O27" t="n">
-        <v>10.17498947896989</v>
+        <v>10.15907500224382</v>
       </c>
       <c r="P27" t="n">
-        <v>379.7138455353332</v>
+        <v>379.6690862722514</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28711,28 +28829,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.02757809546086133</v>
+        <v>-0.02278106986612707</v>
       </c>
       <c r="J28" t="n">
+        <v>221</v>
+      </c>
+      <c r="K28" t="n">
         <v>220</v>
       </c>
-      <c r="K28" t="n">
-        <v>219</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.0004254006673450883</v>
+        <v>0.0002929670216953451</v>
       </c>
       <c r="M28" t="n">
-        <v>8.803659752241748</v>
+        <v>8.788351331378459</v>
       </c>
       <c r="N28" t="n">
-        <v>116.9569289043773</v>
+        <v>116.5711576082266</v>
       </c>
       <c r="O28" t="n">
-        <v>10.81466268102604</v>
+        <v>10.79681238182023</v>
       </c>
       <c r="P28" t="n">
-        <v>376.2392705577668</v>
+        <v>376.1946845430884</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -28789,28 +28907,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.02013545486370998</v>
+        <v>-0.01341937208703103</v>
       </c>
       <c r="J29" t="n">
+        <v>221</v>
+      </c>
+      <c r="K29" t="n">
         <v>220</v>
       </c>
-      <c r="K29" t="n">
-        <v>219</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.0001743557006450569</v>
+        <v>7.810656972673247e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>10.12419732817744</v>
+        <v>10.11078991646906</v>
       </c>
       <c r="N29" t="n">
-        <v>152.1568049074548</v>
+        <v>151.7510722619356</v>
       </c>
       <c r="O29" t="n">
-        <v>12.33518564543943</v>
+        <v>12.31872851644745</v>
       </c>
       <c r="P29" t="n">
-        <v>369.6845375814594</v>
+        <v>369.6221148656849</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28867,28 +28985,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.04174376051662288</v>
+        <v>-0.03350833788657345</v>
       </c>
       <c r="J30" t="n">
+        <v>221</v>
+      </c>
+      <c r="K30" t="n">
         <v>220</v>
       </c>
-      <c r="K30" t="n">
-        <v>219</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.0005132461719000725</v>
+        <v>0.000333556824769432</v>
       </c>
       <c r="M30" t="n">
-        <v>12.50565660067131</v>
+        <v>12.49457223516299</v>
       </c>
       <c r="N30" t="n">
-        <v>222.0827540683958</v>
+        <v>221.5031573080763</v>
       </c>
       <c r="O30" t="n">
-        <v>14.90244121170742</v>
+        <v>14.88298213759851</v>
       </c>
       <c r="P30" t="n">
-        <v>359.7010735632441</v>
+        <v>359.6245293241076</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28945,28 +29063,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2454691605515048</v>
+        <v>-0.2377564874234903</v>
       </c>
       <c r="J31" t="n">
+        <v>221</v>
+      </c>
+      <c r="K31" t="n">
         <v>220</v>
       </c>
-      <c r="K31" t="n">
-        <v>219</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.02186680939336916</v>
+        <v>0.02070743530773744</v>
       </c>
       <c r="M31" t="n">
-        <v>10.93269059477503</v>
+        <v>10.92114925827412</v>
       </c>
       <c r="N31" t="n">
-        <v>176.3952237258164</v>
+        <v>175.9704569113201</v>
       </c>
       <c r="O31" t="n">
-        <v>13.2813863630954</v>
+        <v>13.26538566764344</v>
       </c>
       <c r="P31" t="n">
-        <v>352.0580414783374</v>
+        <v>351.9863559410175</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -29023,28 +29141,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3135828758409935</v>
+        <v>-0.3138279278883028</v>
       </c>
       <c r="J32" t="n">
+        <v>221</v>
+      </c>
+      <c r="K32" t="n">
         <v>220</v>
       </c>
-      <c r="K32" t="n">
-        <v>219</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.06385963134731976</v>
+        <v>0.06504056003614289</v>
       </c>
       <c r="M32" t="n">
-        <v>7.985511899300771</v>
+        <v>7.947600771880218</v>
       </c>
       <c r="N32" t="n">
-        <v>94.34081285011435</v>
+        <v>93.19241008623351</v>
       </c>
       <c r="O32" t="n">
-        <v>9.712919893117329</v>
+        <v>9.653621604674253</v>
       </c>
       <c r="P32" t="n">
-        <v>351.2540191930457</v>
+        <v>351.2559413997791</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -29101,28 +29219,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7551079169187035</v>
+        <v>-0.7557619067781892</v>
       </c>
       <c r="J33" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K33" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2058482662729182</v>
+        <v>0.2083713800167077</v>
       </c>
       <c r="M33" t="n">
-        <v>9.463548791306392</v>
+        <v>9.416773029644471</v>
       </c>
       <c r="N33" t="n">
-        <v>147.2781976979633</v>
+        <v>146.1047781501928</v>
       </c>
       <c r="O33" t="n">
-        <v>12.1358229097974</v>
+        <v>12.08738094668125</v>
       </c>
       <c r="P33" t="n">
-        <v>348.5548058313457</v>
+        <v>348.5604854226286</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -29160,7 +29278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH221"/>
+  <dimension ref="A1:AH222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66782,7 +66900,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>-35.28751975539714,173.15555446626752</t>
+          <t>-35.28749106823411,173.15559830162897</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -66807,17 +66925,17 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>-35.28462248154034,173.1528026685809</t>
+          <t>-35.284576445692934,173.15287281051565</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>-35.284044951230186,173.15225824978702</t>
+          <t>-35.28399617567403,173.1523313471457</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>-35.28345163238659,173.15173496797635</t>
+          <t>-35.28341072083446,173.15179545109842</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -66832,12 +66950,12 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>-35.2816653929752,173.15015192196915</t>
+          <t>-35.28160824369942,173.15023641054253</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>-35.28109845130057,173.14958213647193</t>
+          <t>-35.28106499962081,173.14963159095223</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
@@ -66897,17 +67015,189 @@
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>-35.2741781695533,173.14292561268232</t>
+          <t>-35.2741247237543,173.14299548738998</t>
         </is>
       </c>
       <c r="AG221" t="inlineStr">
         <is>
-          <t>-35.2735296567595,173.1424595826747</t>
+          <t>-35.27348174632595,173.14252222030137</t>
         </is>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>-35.2914665066629,173.1595762560996</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>-35.29096351271899,173.1589087860472</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>-35.2904202386062,173.15830285945688</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-35.289848216252445,173.15774085530683</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-35.28925121480361,173.15721701422555</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-35.288660396982586,173.1566837180616</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-35.28806344404892,173.1561597904358</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-35.287477793384646,173.15561858621714</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-35.28690513231841,173.1550575270946</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-35.286331848451304,173.15449741343937</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-35.28575557935013,173.15394185516396</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-35.28515281323334,173.15342677938804</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-35.28456016127691,173.15289762202553</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-35.28398223166209,173.1523522442741</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-35.28340848303481,173.15179875943014</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>-35.28287380011663,173.15118130047196</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>-35.28221735478196,173.15074384762818</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>-35.28160824369942,173.15023641054253</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>-35.2810682701976,173.14962675578187</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>-35.28051205445203,173.14904110740594</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>-35.27993718681082,173.14848302788553</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>-35.27935485618386,173.14793597571116</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>-35.27879002189639,173.14736305134758</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>-35.278225126270115,173.14679021182096</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>-35.27762471029579,173.1462698793123</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>-35.27702615122055,173.14575545024678</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>-35.27645108559745,173.14520678135244</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>-35.275890840076116,173.14462812511064</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>-35.275300641210244,173.1440858696242</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>-35.27467974925839,173.1435837374499</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>-35.27412189463147,173.14299918616365</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>-35.273487404555986,173.14251482279346</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0067/nzd0067.xlsx
+++ b/data/nzd0067/nzd0067.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH222"/>
+  <dimension ref="A1:AH223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24334,6 +24334,114 @@
         <v>335.2</v>
       </c>
       <c r="AH222" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>420.52</v>
+      </c>
+      <c r="C223" t="n">
+        <v>434.14</v>
+      </c>
+      <c r="D223" t="n">
+        <v>440.9</v>
+      </c>
+      <c r="E223" t="n">
+        <v>441.16</v>
+      </c>
+      <c r="F223" t="n">
+        <v>436.69</v>
+      </c>
+      <c r="G223" t="n">
+        <v>432.66</v>
+      </c>
+      <c r="H223" t="n">
+        <v>427.79</v>
+      </c>
+      <c r="I223" t="n">
+        <v>424.45</v>
+      </c>
+      <c r="J223" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="K223" t="n">
+        <v>423.64</v>
+      </c>
+      <c r="L223" t="n">
+        <v>422.47</v>
+      </c>
+      <c r="M223" t="n">
+        <v>417.37</v>
+      </c>
+      <c r="N223" t="n">
+        <v>414.43</v>
+      </c>
+      <c r="O223" t="n">
+        <v>414.41</v>
+      </c>
+      <c r="P223" t="n">
+        <v>412.01</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>415.68</v>
+      </c>
+      <c r="R223" t="n">
+        <v>401.12</v>
+      </c>
+      <c r="S223" t="n">
+        <v>394.57</v>
+      </c>
+      <c r="T223" t="n">
+        <v>398.8</v>
+      </c>
+      <c r="U223" t="n">
+        <v>400.41</v>
+      </c>
+      <c r="V223" t="n">
+        <v>399.24</v>
+      </c>
+      <c r="W223" t="n">
+        <v>396.49</v>
+      </c>
+      <c r="X223" t="n">
+        <v>395.92</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>395.83</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>348.22</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="AH223" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24350,7 +24458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B228"/>
+  <dimension ref="A1:B229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26633,6 +26741,16 @@
       </c>
       <c r="B228" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -26801,28 +26919,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1919769029493738</v>
+        <v>0.1945328055387296</v>
       </c>
       <c r="J2" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01901202789466272</v>
+        <v>0.01970155659634787</v>
       </c>
       <c r="M2" t="n">
-        <v>8.860485882500386</v>
+        <v>8.833969630402938</v>
       </c>
       <c r="N2" t="n">
-        <v>124.8822475129827</v>
+        <v>124.354026330912</v>
       </c>
       <c r="O2" t="n">
-        <v>11.17507259542338</v>
+        <v>11.15141364719792</v>
       </c>
       <c r="P2" t="n">
-        <v>412.29229336373</v>
+        <v>412.2683635816155</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26879,28 +26997,28 @@
         <v>0.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.203525928036638</v>
+        <v>0.2094354339992147</v>
       </c>
       <c r="J3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02269744027772069</v>
+        <v>0.02419726279914058</v>
       </c>
       <c r="M3" t="n">
-        <v>8.186940742267261</v>
+        <v>8.179601887139006</v>
       </c>
       <c r="N3" t="n">
-        <v>116.5014284936553</v>
+        <v>116.1881777949607</v>
       </c>
       <c r="O3" t="n">
-        <v>10.79358274594934</v>
+        <v>10.77906200905073</v>
       </c>
       <c r="P3" t="n">
-        <v>421.647488919</v>
+        <v>421.5916827037973</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26957,28 +27075,28 @@
         <v>0.0434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3023055213316399</v>
+        <v>0.308301127873652</v>
       </c>
       <c r="J4" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K4" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03510409656001723</v>
+        <v>0.03677064996710522</v>
       </c>
       <c r="M4" t="n">
-        <v>9.684565141110831</v>
+        <v>9.669903943918763</v>
       </c>
       <c r="N4" t="n">
-        <v>161.6911952742067</v>
+        <v>161.1652700676853</v>
       </c>
       <c r="O4" t="n">
-        <v>12.71578527949441</v>
+        <v>12.69508842299593</v>
       </c>
       <c r="P4" t="n">
-        <v>425.7376278341754</v>
+        <v>425.6801222940928</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27035,28 +27153,28 @@
         <v>0.0469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3480047214405006</v>
+        <v>0.3515628531416339</v>
       </c>
       <c r="J5" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04742627756776463</v>
+        <v>0.04880195047654468</v>
       </c>
       <c r="M5" t="n">
-        <v>9.737821959367286</v>
+        <v>9.709535547651434</v>
       </c>
       <c r="N5" t="n">
-        <v>159.8682743325695</v>
+        <v>159.2231673724526</v>
       </c>
       <c r="O5" t="n">
-        <v>12.64390265434567</v>
+        <v>12.61836627192493</v>
       </c>
       <c r="P5" t="n">
-        <v>427.5213777208407</v>
+        <v>427.4881336390439</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27113,28 +27231,28 @@
         <v>0.045</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4699179577148262</v>
+        <v>0.4697981573107167</v>
       </c>
       <c r="J6" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08105276634215941</v>
+        <v>0.08177810334337787</v>
       </c>
       <c r="M6" t="n">
-        <v>9.622404250696059</v>
+        <v>9.578709796268647</v>
       </c>
       <c r="N6" t="n">
-        <v>162.3524041974941</v>
+        <v>161.604327642044</v>
       </c>
       <c r="O6" t="n">
-        <v>12.74175828516199</v>
+        <v>12.71236908062553</v>
       </c>
       <c r="P6" t="n">
-        <v>424.1779345099526</v>
+        <v>424.1790732673988</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27191,28 +27309,28 @@
         <v>0.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5634520125952284</v>
+        <v>0.5617563487220087</v>
       </c>
       <c r="J7" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K7" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1310573782988899</v>
+        <v>0.1315162869923668</v>
       </c>
       <c r="M7" t="n">
-        <v>9.448975076424865</v>
+        <v>9.416119666944454</v>
       </c>
       <c r="N7" t="n">
-        <v>139.554454774474</v>
+        <v>138.9445554914831</v>
       </c>
       <c r="O7" t="n">
-        <v>11.81331684051833</v>
+        <v>11.78747451710854</v>
       </c>
       <c r="P7" t="n">
-        <v>419.546557745629</v>
+        <v>419.5622292954373</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27269,28 +27387,28 @@
         <v>0.0427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6243844888441658</v>
+        <v>0.6194564683611018</v>
       </c>
       <c r="J8" t="n">
+        <v>222</v>
+      </c>
+      <c r="K8" t="n">
         <v>221</v>
       </c>
-      <c r="K8" t="n">
-        <v>220</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.163368178435357</v>
+        <v>0.1624298106703415</v>
       </c>
       <c r="M8" t="n">
-        <v>9.156642588537697</v>
+        <v>9.138636616135132</v>
       </c>
       <c r="N8" t="n">
-        <v>132.8446184847469</v>
+        <v>132.4025183951737</v>
       </c>
       <c r="O8" t="n">
-        <v>11.52582398289801</v>
+        <v>11.50662932379303</v>
       </c>
       <c r="P8" t="n">
-        <v>416.9527297375096</v>
+        <v>416.998224218771</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27347,28 +27465,28 @@
         <v>0.0432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6870039406130852</v>
+        <v>0.6800367936785335</v>
       </c>
       <c r="J9" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K9" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1874299731718583</v>
+        <v>0.1855279362633545</v>
       </c>
       <c r="M9" t="n">
-        <v>9.080126796076462</v>
+        <v>9.075282617807273</v>
       </c>
       <c r="N9" t="n">
-        <v>135.6564423237713</v>
+        <v>135.361487109777</v>
       </c>
       <c r="O9" t="n">
-        <v>11.64716456154764</v>
+        <v>11.63449556748281</v>
       </c>
       <c r="P9" t="n">
-        <v>414.3943602820586</v>
+        <v>414.4587515755991</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27425,28 +27543,28 @@
         <v>0.0369</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8398677891411656</v>
+        <v>0.8331242464251809</v>
       </c>
       <c r="J10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2625536132068799</v>
+        <v>0.2609691797746425</v>
       </c>
       <c r="M10" t="n">
-        <v>9.032065146019308</v>
+        <v>9.028891339734813</v>
       </c>
       <c r="N10" t="n">
-        <v>131.3513422055732</v>
+        <v>131.0558144238096</v>
       </c>
       <c r="O10" t="n">
-        <v>11.46086132040577</v>
+        <v>11.44796114702569</v>
       </c>
       <c r="P10" t="n">
-        <v>410.0572187126043</v>
+        <v>410.1195434263797</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27503,28 +27621,28 @@
         <v>0.0378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8632559414663933</v>
+        <v>0.8564834991329354</v>
       </c>
       <c r="J11" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K11" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2487313669982766</v>
+        <v>0.2473186528323923</v>
       </c>
       <c r="M11" t="n">
-        <v>9.490306337614781</v>
+        <v>9.479156331400477</v>
       </c>
       <c r="N11" t="n">
-        <v>149.2258507407212</v>
+        <v>148.8523508663693</v>
       </c>
       <c r="O11" t="n">
-        <v>12.21580331950057</v>
+        <v>12.20050617254748</v>
       </c>
       <c r="P11" t="n">
-        <v>408.6055053167038</v>
+        <v>408.6680971245665</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27581,28 +27699,28 @@
         <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7679451582337876</v>
+        <v>0.7621362438395014</v>
       </c>
       <c r="J12" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K12" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2031565276758275</v>
+        <v>0.20213018316091</v>
       </c>
       <c r="M12" t="n">
-        <v>9.718380872307597</v>
+        <v>9.705620000340234</v>
       </c>
       <c r="N12" t="n">
-        <v>150.3335898147361</v>
+        <v>149.8640842055551</v>
       </c>
       <c r="O12" t="n">
-        <v>12.26105989768976</v>
+        <v>12.24189871733773</v>
       </c>
       <c r="P12" t="n">
-        <v>408.7049204714501</v>
+        <v>408.7596566601598</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27659,28 +27777,28 @@
         <v>0.0375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7262113617462511</v>
+        <v>0.7199665757411152</v>
       </c>
       <c r="J13" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K13" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1791266740599947</v>
+        <v>0.1778543426446051</v>
       </c>
       <c r="M13" t="n">
-        <v>10.02324963207609</v>
+        <v>10.01704294095254</v>
       </c>
       <c r="N13" t="n">
-        <v>160.2293870704108</v>
+        <v>159.7615918351808</v>
       </c>
       <c r="O13" t="n">
-        <v>12.65817471322034</v>
+        <v>12.63968321735876</v>
       </c>
       <c r="P13" t="n">
-        <v>405.3825670864926</v>
+        <v>405.4402822247739</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27737,28 +27855,28 @@
         <v>0.0353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7264468755967405</v>
+        <v>0.71892136964148</v>
       </c>
       <c r="J14" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K14" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1843329772085383</v>
+        <v>0.1823818454227861</v>
       </c>
       <c r="M14" t="n">
-        <v>9.863485209189077</v>
+        <v>9.859980711122818</v>
       </c>
       <c r="N14" t="n">
-        <v>154.8166973589691</v>
+        <v>154.4881321282888</v>
       </c>
       <c r="O14" t="n">
-        <v>12.44253580902901</v>
+        <v>12.42932548967516</v>
       </c>
       <c r="P14" t="n">
-        <v>403.9903531450757</v>
+        <v>404.0599048665418</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27815,28 +27933,28 @@
         <v>0.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6558669411850661</v>
+        <v>0.6500607917102664</v>
       </c>
       <c r="J15" t="n">
+        <v>222</v>
+      </c>
+      <c r="K15" t="n">
         <v>221</v>
       </c>
-      <c r="K15" t="n">
-        <v>220</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1564715925552647</v>
+        <v>0.1552892369478908</v>
       </c>
       <c r="M15" t="n">
-        <v>9.541170436178676</v>
+        <v>9.535672244476544</v>
       </c>
       <c r="N15" t="n">
-        <v>152.1716556145727</v>
+        <v>151.6995424104544</v>
       </c>
       <c r="O15" t="n">
-        <v>12.33578759603831</v>
+        <v>12.31663681410045</v>
       </c>
       <c r="P15" t="n">
-        <v>403.7210794463263</v>
+        <v>403.7752784297596</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27893,28 +28011,28 @@
         <v>0.0309</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4254614596553496</v>
+        <v>0.4236154444232939</v>
       </c>
       <c r="J16" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K16" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07319282543271821</v>
+        <v>0.07328918519670657</v>
       </c>
       <c r="M16" t="n">
-        <v>9.791918328904119</v>
+        <v>9.759320616049612</v>
       </c>
       <c r="N16" t="n">
-        <v>148.9685886113797</v>
+        <v>148.3130533539029</v>
       </c>
       <c r="O16" t="n">
-        <v>12.20526888730354</v>
+        <v>12.17838467753022</v>
       </c>
       <c r="P16" t="n">
-        <v>402.7487580305618</v>
+        <v>402.7661526470503</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27971,28 +28089,28 @@
         <v>0.0256</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02325414055574002</v>
+        <v>0.03537176482560075</v>
       </c>
       <c r="J17" t="n">
+        <v>222</v>
+      </c>
+      <c r="K17" t="n">
         <v>221</v>
       </c>
-      <c r="K17" t="n">
-        <v>220</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.0002187603029941698</v>
+        <v>0.0005082464990896485</v>
       </c>
       <c r="M17" t="n">
-        <v>10.47309777108337</v>
+        <v>10.48348797395268</v>
       </c>
       <c r="N17" t="n">
-        <v>164.3515082539523</v>
+        <v>164.5624032089533</v>
       </c>
       <c r="O17" t="n">
-        <v>12.81996522046579</v>
+        <v>12.8281878380757</v>
       </c>
       <c r="P17" t="n">
-        <v>400.416928410029</v>
+        <v>400.3052794641137</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28049,28 +28167,28 @@
         <v>0.0209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2650847137530387</v>
+        <v>0.2725949424908361</v>
       </c>
       <c r="J18" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K18" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01758200366640672</v>
+        <v>0.01873413865619578</v>
       </c>
       <c r="M18" t="n">
-        <v>13.12025941541479</v>
+        <v>13.09296232692102</v>
       </c>
       <c r="N18" t="n">
-        <v>260.313998956075</v>
+        <v>259.5087247743231</v>
       </c>
       <c r="O18" t="n">
-        <v>16.13424925294248</v>
+        <v>16.10927449559176</v>
       </c>
       <c r="P18" t="n">
-        <v>384.8892263977357</v>
+        <v>384.8198158703341</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28127,28 +28245,28 @@
         <v>0.0255</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2493614241395408</v>
+        <v>0.2491085354420657</v>
       </c>
       <c r="J19" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K19" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01722578368645944</v>
+        <v>0.01736439050683536</v>
       </c>
       <c r="M19" t="n">
-        <v>11.9201778947056</v>
+        <v>11.86800748424589</v>
       </c>
       <c r="N19" t="n">
-        <v>235.1979409370248</v>
+        <v>234.1389072256865</v>
       </c>
       <c r="O19" t="n">
-        <v>15.33616447932875</v>
+        <v>15.30159819187808</v>
       </c>
       <c r="P19" t="n">
-        <v>388.1624344863433</v>
+        <v>388.164771717136</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28205,28 +28323,28 @@
         <v>0.0308</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5791668331038166</v>
+        <v>0.5799094176318896</v>
       </c>
       <c r="J20" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K20" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1377725611311115</v>
+        <v>0.13929512738316</v>
       </c>
       <c r="M20" t="n">
-        <v>9.264029877939583</v>
+        <v>9.225080027642088</v>
       </c>
       <c r="N20" t="n">
-        <v>136.9153751598266</v>
+        <v>136.2908433997084</v>
       </c>
       <c r="O20" t="n">
-        <v>11.70108435829033</v>
+        <v>11.67436693785613</v>
       </c>
       <c r="P20" t="n">
-        <v>382.3313967771178</v>
+        <v>382.3243896439209</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28283,28 +28401,28 @@
         <v>0.0381</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5837680927656032</v>
+        <v>0.5862854926923893</v>
       </c>
       <c r="J21" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K21" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1625392421180822</v>
+        <v>0.1650605618571978</v>
       </c>
       <c r="M21" t="n">
-        <v>8.264547284393213</v>
+        <v>8.237500963731316</v>
       </c>
       <c r="N21" t="n">
-        <v>115.2300262723986</v>
+        <v>114.732522349032</v>
       </c>
       <c r="O21" t="n">
-        <v>10.73452496724464</v>
+        <v>10.71132682486311</v>
       </c>
       <c r="P21" t="n">
-        <v>381.7104634381947</v>
+        <v>381.6866407068551</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28361,28 +28479,28 @@
         <v>0.0421</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4347977983254425</v>
+        <v>0.4386001143565881</v>
       </c>
       <c r="J22" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K22" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1023880660776687</v>
+        <v>0.10486090077497</v>
       </c>
       <c r="M22" t="n">
-        <v>8.107830791938174</v>
+        <v>8.089995693408932</v>
       </c>
       <c r="N22" t="n">
-        <v>110.7626309324229</v>
+        <v>110.3457457445549</v>
       </c>
       <c r="O22" t="n">
-        <v>10.5243826865248</v>
+        <v>10.50455833172223</v>
       </c>
       <c r="P22" t="n">
-        <v>382.9536905800075</v>
+        <v>382.9183313368483</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28439,28 +28557,28 @@
         <v>0.0526</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3637727884296957</v>
+        <v>0.3683874750216114</v>
       </c>
       <c r="J23" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K23" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07195225105559377</v>
+        <v>0.07427324692999782</v>
       </c>
       <c r="M23" t="n">
-        <v>8.052915402641236</v>
+        <v>8.040731690799978</v>
       </c>
       <c r="N23" t="n">
-        <v>110.9276292239788</v>
+        <v>110.5583589869679</v>
       </c>
       <c r="O23" t="n">
-        <v>10.53221862780956</v>
+        <v>10.51467350833909</v>
       </c>
       <c r="P23" t="n">
-        <v>381.2057031762673</v>
+        <v>381.1622199470463</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -28517,28 +28635,28 @@
         <v>0.0468</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5847273060118066</v>
+        <v>0.5875591679061327</v>
       </c>
       <c r="J24" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K24" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1853587501360103</v>
+        <v>0.18830636204456</v>
       </c>
       <c r="M24" t="n">
-        <v>8.019582436023363</v>
+        <v>7.999232076473841</v>
       </c>
       <c r="N24" t="n">
-        <v>97.659260702971</v>
+        <v>97.26617332344357</v>
       </c>
       <c r="O24" t="n">
-        <v>9.882270017712074</v>
+        <v>9.862361447617076</v>
       </c>
       <c r="P24" t="n">
-        <v>376.8071828668548</v>
+        <v>376.7804988228964</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -28595,28 +28713,28 @@
         <v>0.0457</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4956614079625534</v>
+        <v>0.5008308950704672</v>
       </c>
       <c r="J25" t="n">
+        <v>222</v>
+      </c>
+      <c r="K25" t="n">
         <v>221</v>
       </c>
-      <c r="K25" t="n">
-        <v>220</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1418337653470392</v>
+        <v>0.1454238327918098</v>
       </c>
       <c r="M25" t="n">
-        <v>8.307516187832256</v>
+        <v>8.298923857605114</v>
       </c>
       <c r="N25" t="n">
-        <v>97.84775565113364</v>
+        <v>97.57744593168667</v>
       </c>
       <c r="O25" t="n">
-        <v>9.891802447033283</v>
+        <v>9.878129677812833</v>
       </c>
       <c r="P25" t="n">
-        <v>376.2699978494056</v>
+        <v>376.2218497474788</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -28673,28 +28791,28 @@
         <v>0.0465</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3384257730070798</v>
+        <v>0.3414939970418513</v>
       </c>
       <c r="J26" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K26" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07330617772968173</v>
+        <v>0.07520316018643569</v>
       </c>
       <c r="M26" t="n">
-        <v>8.217019555424216</v>
+        <v>8.197908736670451</v>
       </c>
       <c r="N26" t="n">
-        <v>95.64784719891146</v>
+        <v>95.27415934393633</v>
       </c>
       <c r="O26" t="n">
-        <v>9.779971738144823</v>
+        <v>9.760848290181357</v>
       </c>
       <c r="P26" t="n">
-        <v>377.2616467476362</v>
+        <v>377.233100307056</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -28751,28 +28869,28 @@
         <v>0.0476</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05847554464669615</v>
+        <v>0.06174684599842344</v>
       </c>
       <c r="J27" t="n">
+        <v>222</v>
+      </c>
+      <c r="K27" t="n">
         <v>221</v>
       </c>
-      <c r="K27" t="n">
-        <v>220</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.00217612068331674</v>
+        <v>0.002448985228529321</v>
       </c>
       <c r="M27" t="n">
-        <v>8.488733474350008</v>
+        <v>8.471313446804791</v>
       </c>
       <c r="N27" t="n">
-        <v>103.2068049012153</v>
+        <v>102.8088591699096</v>
       </c>
       <c r="O27" t="n">
-        <v>10.15907500224382</v>
+        <v>10.1394703594374</v>
       </c>
       <c r="P27" t="n">
-        <v>379.6690862722514</v>
+        <v>379.6386176884968</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -28829,28 +28947,28 @@
         <v>0.0477</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.02278106986612707</v>
+        <v>-0.01865215980330475</v>
       </c>
       <c r="J28" t="n">
+        <v>222</v>
+      </c>
+      <c r="K28" t="n">
         <v>221</v>
       </c>
-      <c r="K28" t="n">
-        <v>220</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.0002929670216953451</v>
+        <v>0.000198239944304901</v>
       </c>
       <c r="M28" t="n">
-        <v>8.788351331378459</v>
+        <v>8.770473520381767</v>
       </c>
       <c r="N28" t="n">
-        <v>116.5711576082266</v>
+        <v>116.1536918875675</v>
       </c>
       <c r="O28" t="n">
-        <v>10.79681238182023</v>
+        <v>10.77746221925957</v>
       </c>
       <c r="P28" t="n">
-        <v>376.1946845430884</v>
+        <v>376.1562282749128</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -28907,28 +29025,28 @@
         <v>0.045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01341937208703103</v>
+        <v>-0.007348432797638761</v>
       </c>
       <c r="J29" t="n">
+        <v>222</v>
+      </c>
+      <c r="K29" t="n">
         <v>221</v>
       </c>
-      <c r="K29" t="n">
-        <v>220</v>
-      </c>
       <c r="L29" t="n">
-        <v>7.810656972673247e-05</v>
+        <v>2.362576440340103e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>10.11078991646906</v>
+        <v>10.09427136361326</v>
       </c>
       <c r="N29" t="n">
-        <v>151.7510722619356</v>
+        <v>151.302239811254</v>
       </c>
       <c r="O29" t="n">
-        <v>12.31872851644745</v>
+        <v>12.30049754324003</v>
       </c>
       <c r="P29" t="n">
-        <v>369.6221148656849</v>
+        <v>369.5655707255033</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -28985,28 +29103,28 @@
         <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.03350833788657345</v>
+        <v>-0.02609570934067347</v>
       </c>
       <c r="J30" t="n">
+        <v>222</v>
+      </c>
+      <c r="K30" t="n">
         <v>221</v>
       </c>
-      <c r="K30" t="n">
-        <v>220</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.000333556824769432</v>
+        <v>0.000204076739735326</v>
       </c>
       <c r="M30" t="n">
-        <v>12.49457223516299</v>
+        <v>12.47889658911005</v>
       </c>
       <c r="N30" t="n">
-        <v>221.5031573080763</v>
+        <v>220.8554394423687</v>
       </c>
       <c r="O30" t="n">
-        <v>14.88298213759851</v>
+        <v>14.86120585424913</v>
       </c>
       <c r="P30" t="n">
-        <v>359.6245293241076</v>
+        <v>359.5554888202194</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -29063,28 +29181,28 @@
         <v>0.0481</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2377564874234903</v>
+        <v>-0.2314074219891627</v>
       </c>
       <c r="J31" t="n">
+        <v>222</v>
+      </c>
+      <c r="K31" t="n">
         <v>221</v>
       </c>
-      <c r="K31" t="n">
-        <v>220</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.02070743530773744</v>
+        <v>0.01980632621723355</v>
       </c>
       <c r="M31" t="n">
-        <v>10.92114925827412</v>
+        <v>10.90288381457872</v>
       </c>
       <c r="N31" t="n">
-        <v>175.9704569113201</v>
+        <v>175.434324350414</v>
       </c>
       <c r="O31" t="n">
-        <v>13.26538566764344</v>
+        <v>13.2451622998895</v>
       </c>
       <c r="P31" t="n">
-        <v>351.9863559410175</v>
+        <v>351.9272213608761</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -29141,28 +29259,28 @@
         <v>0.0455</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3138279278883028</v>
+        <v>-0.3093328986080775</v>
       </c>
       <c r="J32" t="n">
+        <v>222</v>
+      </c>
+      <c r="K32" t="n">
         <v>221</v>
       </c>
-      <c r="K32" t="n">
-        <v>220</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.06504056003614289</v>
+        <v>0.06383182368324336</v>
       </c>
       <c r="M32" t="n">
-        <v>7.947600771880218</v>
+        <v>7.93505983296188</v>
       </c>
       <c r="N32" t="n">
-        <v>93.19241008623351</v>
+        <v>92.90110435589604</v>
       </c>
       <c r="O32" t="n">
-        <v>9.653621604674253</v>
+        <v>9.638521896841654</v>
       </c>
       <c r="P32" t="n">
-        <v>351.2559413997791</v>
+        <v>351.214075132695</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -29219,28 +29337,28 @@
         <v>0.0372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7557619067781892</v>
+        <v>-0.7515088191584574</v>
       </c>
       <c r="J33" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K33" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2083713800167077</v>
+        <v>0.2080514694268653</v>
       </c>
       <c r="M33" t="n">
-        <v>9.416773029644471</v>
+        <v>9.389250789900908</v>
       </c>
       <c r="N33" t="n">
-        <v>146.1047781501928</v>
+        <v>145.5481775868035</v>
       </c>
       <c r="O33" t="n">
-        <v>12.08738094668125</v>
+        <v>12.06433494175305</v>
       </c>
       <c r="P33" t="n">
-        <v>348.5604854226286</v>
+        <v>348.5213411611456</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -29278,7 +29396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH222"/>
+  <dimension ref="A1:AH223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67201,6 +67319,178 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>-35.29144923755039,173.15960264398382</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>-35.2909526563055,173.15892537513528</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>-35.29041748232895,173.1583070711806</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-35.2898457412392,173.1577446372475</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-35.28924738979857,173.15722285901555</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-35.28865150950751,173.15669729854085</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-35.288050900384455,173.15617895773065</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-35.287458893593076,173.1556474659583</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-35.286885951366614,173.1550868364744</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-35.2863078864308,173.15453402852452</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-35.28572807377204,173.15398388497937</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-35.285126151489855,173.15346751974965</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-35.28453688976696,173.15293307928715</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-35.28396777541729,173.15237390904457</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-35.28339063801375,173.15182514124825</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>-35.282845913822314,173.151222527233</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>-35.28219658356886,173.15077455544358</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>-35.28159321044634,173.15025863542863</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>-35.281051687797486,173.14965127093993</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>-35.28049512785884,173.14906613143907</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>-35.27992261278996,173.14850457391537</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>-35.27934102813493,173.14795641890493</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>-35.27877194797058,173.14738977160135</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>-35.27820561799262,173.1468190526193</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>-35.27760669389685,173.14629651451352</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>-35.27701615071336,173.14576961726436</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>-35.27644712840462,173.14521205363778</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>-35.275887334387406,173.14463270843007</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>-35.275296089980934,173.14409181987384</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>-35.27467101584438,173.14359515544</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>-35.274103874346444,173.14302274573782</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>-35.27347596509042,173.14252977862358</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
